--- a/public/templates/membri-template.xlsx
+++ b/public/templates/membri-template.xlsx
@@ -60,9 +60,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:J4"/>
   <sheetData>
-    <row r="1" spans="1:6" customHeight="0">
+    <row r="1" spans="1:10" customHeight="0">
       <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Prenume</t>
@@ -90,11 +90,31 @@
       </c>
       <c r="F1" s="0" t="inlineStr">
         <is>
+          <t>Abonament</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Data start</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Data expirare</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="2" spans="1:6" customHeight="0">
+    <row r="2" spans="1:10" customHeight="0">
       <c r="A2" s="0" t="inlineStr">
         <is>
           <t>Andrei</t>
@@ -122,11 +142,31 @@
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
+          <t>Lunar</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
           <t>Abonament anual</t>
         </is>
       </c>
     </row>
-    <row r="3" spans="1:6" customHeight="0">
+    <row r="3" spans="1:10" customHeight="0">
       <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Maria</t>
@@ -152,8 +192,28 @@
           <t>22/07/1985</t>
         </is>
       </c>
-    </row>
-    <row r="4" spans="1:6" customHeight="0">
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>Trimestrial</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:10" customHeight="0">
       <c r="A4" s="0" t="inlineStr">
         <is>
           <t>George</t>
@@ -180,6 +240,16 @@
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>Lunar</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>Preferă antrenament dimineața</t>
         </is>
